--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56170,6 +56170,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2427">
+      <c r="A2427" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2427" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2427" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="D2427" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="E2427" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="F2427" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="G2427" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56193,6 +56193,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2428">
+      <c r="A2428" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2428" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2428" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="D2428" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="E2428" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="F2428" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="G2428" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56216,6 +56216,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2429">
+      <c r="A2429" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2429" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2429" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="D2429" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="E2429" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="F2429" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="G2429" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56239,6 +56239,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2430">
+      <c r="A2430" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2430" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2430" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="D2430" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="E2430" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="F2430" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="G2430" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56103,7 +56103,7 @@
     </row>
     <row r="2424">
       <c r="A2424" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2424" t="n">
         <v>0</v>
@@ -56126,7 +56126,7 @@
     </row>
     <row r="2425">
       <c r="A2425" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2425" t="n">
         <v>0</v>
@@ -56149,7 +56149,7 @@
     </row>
     <row r="2426">
       <c r="A2426" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2426" t="n">
         <v>0</v>
@@ -56172,7 +56172,7 @@
     </row>
     <row r="2427">
       <c r="A2427" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2427" t="n">
         <v>0</v>
@@ -56195,7 +56195,7 @@
     </row>
     <row r="2428">
       <c r="A2428" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2428" t="n">
         <v>0</v>
@@ -56218,7 +56218,7 @@
     </row>
     <row r="2429">
       <c r="A2429" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2429" t="n">
         <v>0</v>
@@ -56241,7 +56241,7 @@
     </row>
     <row r="2430">
       <c r="A2430" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2430" t="n">
         <v>0</v>
@@ -56259,6 +56259,52 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G2430" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2431" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2431" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="D2431" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="E2431" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="F2431" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="G2431" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2432" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2432" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D2432" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="E2432" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="F2432" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="G2432" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -63659,6 +63659,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2435">
+      <c r="A2435" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2435" t="n">
+        <v>150</v>
+      </c>
+      <c r="C2435" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="D2435" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="E2435" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="F2435" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="G2435" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="H2435" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -63737,6 +63737,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2438">
+      <c r="A2438" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2438" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C2438" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="D2438" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="E2438" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F2438" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="G2438" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="H2438" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56446,6 +56446,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2439">
+      <c r="A2439" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2439" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2439" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="D2439" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="E2439" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="F2439" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="G2439" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56469,6 +56469,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2440">
+      <c r="A2440" s="1" t="n">
+        <v>46294.2916666667</v>
+      </c>
+      <c r="B2440" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2440" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="D2440" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="E2440" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="F2440" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="G2440" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56492,6 +56492,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2441">
+      <c r="A2441" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2441" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2441" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="D2441" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="E2441" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="F2441" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="G2441" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56561,6 +56561,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2444">
+      <c r="A2444" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2444" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2444" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2444" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2444" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2444" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2444" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56584,6 +56584,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2445">
+      <c r="A2445" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2445" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2445" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2445" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2445" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2445" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2445" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56607,6 +56607,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2446">
+      <c r="A2446" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2446" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2446" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2446" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2446" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2446" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2446" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56630,6 +56630,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2447">
+      <c r="A2447" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2447" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2447" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2447" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2447" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2447" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2447" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56676,6 +56676,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2449">
+      <c r="A2449" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2449" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2449" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2449" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2449" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2449" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2449" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56699,6 +56699,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2450">
+      <c r="A2450" s="1" t="n">
+        <v>46308.2916666667</v>
+      </c>
+      <c r="B2450" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2450" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2450" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2450" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2450" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2450" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56722,6 +56722,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2451">
+      <c r="A2451" s="1" t="n">
+        <v>46309.2916666667</v>
+      </c>
+      <c r="B2451" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2451" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2451" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2451" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2451" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2451" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -56745,6 +56745,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2452">
+      <c r="A2452" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2452" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2452" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2452" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2452" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2452" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2452" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -71515,6 +71515,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2454">
+      <c r="A2454" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2454" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2454" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2454" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2454" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2454" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2454" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="H2454" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2454" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -71544,6 +71544,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2455">
+      <c r="A2455" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2455" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2455" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2455" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2455" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2455" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2455" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="H2455" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2455" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -71573,6 +71573,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2456">
+      <c r="A2456" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2456" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2456" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2456" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="E2456" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2456" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="G2456" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="H2456" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2456" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2457" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2457" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="D2457" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E2457" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="F2457" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="G2457" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="H2457" t="n">
+        <v>150</v>
+      </c>
+      <c r="I2457" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -71631,6 +71631,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2458">
+      <c r="A2458" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2458" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2458" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="D2458" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E2458" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="F2458" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="G2458" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="H2458" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I2458" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -71660,6 +71660,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2459">
+      <c r="A2459" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2459" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2459" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="D2459" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E2459" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="F2459" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="G2459" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="H2459" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I2459" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -71689,6 +71689,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2460">
+      <c r="A2460" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2460" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2460" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="D2460" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E2460" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="F2460" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="G2460" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="H2460" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I2460" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -71718,6 +71718,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2461">
+      <c r="A2461" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2461" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2461" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="D2461" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="E2461" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="F2461" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G2461" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2461" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I2461" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TLS.MI.xlsx
+++ b/data/TLS.MI.xlsx
@@ -71747,6 +71747,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2462">
+      <c r="A2462" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2462" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2462" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D2462" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E2462" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F2462" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G2462" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2462" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2462" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
